--- a/test-cases/LiquidPay_Full_TestSuite_50plus.xlsx
+++ b/test-cases/LiquidPay_Full_TestSuite_50plus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RamonJrTan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RamonJrTan\Downloads\fintech-wallet-testing-liquidpay-premium-final\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81E5BEB-F54F-4A7C-B3C5-0D2CC5F1C27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EF6BA9-5B83-4A8C-877F-A5FB1FB9A902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1788,6 +1788,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1800,10 +1804,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2038,14 +2038,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2055,14 +2055,14 @@
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -2098,14 +2098,14 @@
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2318,14 +2318,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -2334,11 +2334,11 @@
       <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
@@ -2434,53 +2434,53 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -2518,427 +2518,427 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K11" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="22" t="s">
+      <c r="K11" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="K12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="22" t="s">
+      <c r="K13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="22" t="s">
+      <c r="K14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="22" t="s">
+      <c r="K15" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="16" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="17" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -2981,55 +2981,54 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="42.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="41.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -3067,320 +3066,320 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="21" t="s">
+      <c r="K11" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="K12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="17" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="20" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="22" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="19" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -3395,53 +3394,53 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="69.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -3479,464 +3478,464 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="21" t="s">
+      <c r="K11" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="K12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="22" t="s">
+      <c r="K13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="22" t="s">
+      <c r="K14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="22" t="s">
+      <c r="K15" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="16" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K16" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="22" t="s">
+      <c r="K16" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="16" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="17" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -3949,55 +3948,55 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="24.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -4035,383 +4034,383 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="21" t="s">
+      <c r="K11" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="K12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="22" t="s">
+      <c r="K13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="22" t="s">
+      <c r="K14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>335</v>
       </c>
     </row>
@@ -4429,53 +4428,53 @@
   <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -4513,443 +4512,443 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="21" t="s">
+      <c r="K11" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K12" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="21" t="s">
+      <c r="K12" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+    <row r="13" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="21" t="s">
+      <c r="K13" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="22" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="21" t="s">
+      <c r="K14" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="15" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-    </row>
-    <row r="16" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-    </row>
-    <row r="17" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-    </row>
-    <row r="18" spans="1:12" s="22" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-    </row>
-    <row r="19" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+    </row>
+    <row r="18" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -4977,53 +4976,53 @@
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -5061,380 +5060,380 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K11" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="22" t="s">
+      <c r="K11" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="K12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="22" t="s">
+      <c r="K13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="17" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="20" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="22" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="23" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="24" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="25" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="26" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="27" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="28" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="29" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="30" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="31" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="32" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="35" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="41" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="42" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="43" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="45" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="19" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="23" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="24" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="25" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="26" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="27" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="28" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="29" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="30" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="31" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="40" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="41" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="43" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="44" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="45" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -5449,53 +5448,53 @@
   <dimension ref="A1:L160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="4" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
@@ -5533,384 +5532,384 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="22" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>470</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="15" t="s">
         <v>473</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="s">
+      <c r="K5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>484</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="15" t="s">
         <v>486</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="15" t="s">
         <v>487</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
+      <c r="K7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="22" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>489</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>490</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="22" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="K9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="22" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>501</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>503</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
         <v>504</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="17" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="20" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="22" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="23" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="24" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="25" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="26" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="27" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="28" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="29" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="30" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="31" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="32" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="35" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="41" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="42" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="43" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="45" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="46" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="47" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="48" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="49" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="50" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="51" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="52" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="53" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="54" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="55" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="56" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="57" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="58" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="59" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="60" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="61" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="62" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="63" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="64" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="65" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="66" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="67" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="68" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="69" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="70" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="71" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="72" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="73" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="74" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="75" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="76" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="77" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="78" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="79" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="80" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="81" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="82" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="83" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="84" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="85" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="86" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="87" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="88" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="89" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="90" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="91" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="92" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="93" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="94" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="95" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="96" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="97" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="98" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="99" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="100" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="101" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="102" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="103" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="104" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="105" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="106" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="107" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="108" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="109" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="110" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="111" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="112" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="113" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="114" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="115" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="116" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="117" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="118" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="119" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="120" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="121" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="122" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="123" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="124" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="125" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="126" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="127" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="128" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="129" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="130" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="131" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="132" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="133" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="134" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="135" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="136" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="137" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="138" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="139" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="140" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="141" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="142" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="143" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="144" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="145" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="146" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="147" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="148" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="149" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="150" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="151" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="152" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="153" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="154" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="155" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="156" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="157" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="158" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="159" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="160" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="19" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="23" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="24" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="25" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="26" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="27" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="28" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="29" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="30" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="31" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="40" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="41" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="43" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="44" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="45" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="46" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="48" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="49" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="51" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="53" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="62" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="63" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="64" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="65" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="66" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="67" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="68" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="69" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="70" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="71" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="72" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="73" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="74" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="75" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="76" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="77" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="78" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="79" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="80" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="81" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="82" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="83" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="84" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="85" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="86" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="87" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="88" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="89" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="90" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="91" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="92" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="93" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="94" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="95" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="96" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="97" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="98" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="99" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="101" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="102" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="103" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="104" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="105" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="106" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="107" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="108" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="109" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="110" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="111" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="113" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="114" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="115" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="116" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="117" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="118" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="119" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="120" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="121" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="122" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="123" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="124" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="125" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="126" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="127" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="128" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="129" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="130" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="131" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="132" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="133" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="134" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="135" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="136" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="137" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="138" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="139" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="140" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="141" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="142" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="143" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="144" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="145" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="146" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="147" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="148" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="149" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="150" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="151" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="152" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="153" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="154" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="155" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="156" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="157" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="158" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="159" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="160" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
